--- a/Tailieu/Soketoan2026/QSocai.xlsx
+++ b/Tailieu/Soketoan2026/QSocai.xlsx
@@ -7,6 +7,7 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="111" sheetId="1" r:id="rId2"/>
+    <x:sheet name="112" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -16,10 +17,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>CÔNG TY TNHH ĐẦU TƯ HAFI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MST:3502348621</x:t>
+    <x:t>CÔNG TY TNHH THIẾT BỊ NỘI THẤT TRƯỜNG THỊNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MST:3502561068</x:t>
   </x:si>
   <x:si>
     <x:t>SỔ CÁI TÀI KHOẢN</x:t>
@@ -34,7 +35,7 @@
     <x:t xml:space="preserve">Số dư đầu kỳ </x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">5.901.937.438 </x:t>
+    <x:t xml:space="preserve">2.507.248.600 </x:t>
   </x:si>
   <x:si>
     <x:t>STT</x:t>
@@ -52,76 +53,52 @@
     <x:t>Phát sinh có</x:t>
   </x:si>
   <x:si>
-    <x:t>Đối ứng theo tài khoản 133</x:t>
-  </x:si>
-  <x:si>
-    <x:t>133</x:t>
-  </x:si>
-  <x:si>
-    <x:t>588.836</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đối ứng theo tài khoản 333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15.170.274</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đối ứng theo tài khoản 511</x:t>
-  </x:si>
-  <x:si>
-    <x:t>511</x:t>
-  </x:si>
-  <x:si>
-    <x:t>188.715.926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đối ứng theo tài khoản 642</x:t>
-  </x:si>
-  <x:si>
-    <x:t>642</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.936.514</x:t>
-  </x:si>
-  <x:si>
     <x:t>Tổng phát sinh</x:t>
   </x:si>
   <x:si>
-    <x:t>203.886.200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.525.350</x:t>
+    <x:t>0</x:t>
   </x:si>
   <x:si>
     <x:t>Phát sinh luỷ kế</x:t>
   </x:si>
   <x:si>
-    <x:t>2.723.845.709</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.885.196.009</x:t>
+    <x:t>191.471.988</x:t>
+  </x:si>
+  <x:si>
+    <x:t>776.543.293</x:t>
   </x:si>
   <x:si>
     <x:t>Số dư cuối kỳ</x:t>
   </x:si>
   <x:si>
-    <x:t>6.740.587.138</x:t>
+    <x:t>1.922.177.295</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>Ngày 31 tháng 5 năm 2026</x:t>
+    <x:t>Ngày 30 tháng 6 năm 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Người lập biểu</x:t>
   </x:si>
   <x:si>
     <x:t>Giám đốc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">33.296.496 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.376.969.140</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.065.719.725</x:t>
+  </x:si>
+  <x:si>
+    <x:t>344.545.911</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -230,7 +207,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="9">
+  <x:cellStyleXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -249,9 +226,6 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -259,7 +233,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -310,18 +284,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -635,7 +597,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E15"/>
+  <x:dimension ref="A1:E11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -710,115 +672,55 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="A7" s="13">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="2"/>
+      <x:c r="C7" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D7" s="15"/>
-      <x:c r="E7" s="15" t="s">
+      <x:c r="E7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="B8" s="2"/>
+      <x:c r="C8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
-      <x:c r="A8" s="13">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="B9" s="2"/>
+      <x:c r="C9" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="15"/>
-    </x:row>
-    <x:row r="9" spans="1:5">
-      <x:c r="A9" s="13">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="s">
+      <x:c r="D9" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="s">
+      <x:c r="E9" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="C10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E9" s="15"/>
-    </x:row>
-    <x:row r="10" spans="1:5">
-      <x:c r="A10" s="13">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="s">
+      <x:c r="D10" s="14"/>
+    </x:row>
+    <x:row r="11" spans="1:5">
+      <x:c r="B11" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C10" s="13" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D10" s="15"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:5">
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:5">
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E12" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:5">
-      <x:c r="B13" s="2"/>
-      <x:c r="C13" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:5">
-      <x:c r="C14" s="17" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D14" s="17"/>
-    </x:row>
-    <x:row r="15" spans="1:5">
-      <x:c r="B15" s="18" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C15" s="19" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="19"/>
+      <x:c r="D11" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="7">
@@ -827,8 +729,156 @@
     <x:mergeCell ref="A3:E3"/>
     <x:mergeCell ref="A4:E4"/>
     <x:mergeCell ref="A5:C5"/>
-    <x:mergeCell ref="C14:D14"/>
-    <x:mergeCell ref="C15:D15"/>
+    <x:mergeCell ref="C10:D10"/>
+    <x:mergeCell ref="C11:D11"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E11"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="5.710625" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="40.710625" style="2" customWidth="1"/>
+    <x:col min="3" max="5" width="15.710625" style="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5">
+      <x:c r="A1" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="3"/>
+      <x:c r="D2" s="3"/>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+      <x:c r="C3" s="5"/>
+      <x:c r="D3" s="5"/>
+      <x:c r="E3" s="5"/>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B4" s="8"/>
+      <x:c r="C4" s="7"/>
+      <x:c r="D4" s="7"/>
+      <x:c r="E4" s="7"/>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="8"/>
+      <x:c r="C5" s="7"/>
+      <x:c r="D5" s="9" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="B7" s="2"/>
+      <x:c r="C7" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="B8" s="2"/>
+      <x:c r="C8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="B9" s="2"/>
+      <x:c r="C9" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="C10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="14"/>
+    </x:row>
+    <x:row r="11" spans="1:5">
+      <x:c r="B11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D11" s="16"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A4:E4"/>
+    <x:mergeCell ref="A5:C5"/>
+    <x:mergeCell ref="C10:D10"/>
+    <x:mergeCell ref="C11:D11"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Tailieu/Soketoan2026/QSocai.xlsx
+++ b/Tailieu/Soketoan2026/QSocai.xlsx
@@ -7,7 +7,6 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="111" sheetId="1" r:id="rId2"/>
-    <x:sheet name="112" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -53,52 +52,94 @@
     <x:t>Phát sinh có</x:t>
   </x:si>
   <x:si>
+    <x:t>Đối ứng theo tài khoản 112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>500.000.000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đối ứng theo tài khoản 133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>447.719</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đối ứng theo tài khoản 156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.581.481</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đối ứng theo tài khoản 333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.703.450</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đối ứng theo tài khoản 511</x:t>
+  </x:si>
+  <x:si>
+    <x:t>511</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46.293.124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đối ứng theo tài khoản 642</x:t>
+  </x:si>
+  <x:si>
+    <x:t>642</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.015.000</x:t>
+  </x:si>
+  <x:si>
     <x:t>Tổng phát sinh</x:t>
   </x:si>
   <x:si>
-    <x:t>0</x:t>
+    <x:t>549.996.574</x:t>
+  </x:si>
+  <x:si>
+    <x:t>506.044.200</x:t>
   </x:si>
   <x:si>
     <x:t>Phát sinh luỷ kế</x:t>
   </x:si>
   <x:si>
-    <x:t>191.471.988</x:t>
-  </x:si>
-  <x:si>
-    <x:t>776.543.293</x:t>
+    <x:t>953.107.562</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.378.618.651</x:t>
   </x:si>
   <x:si>
     <x:t>Số dư cuối kỳ</x:t>
   </x:si>
   <x:si>
-    <x:t>1.922.177.295</x:t>
+    <x:t>2.081.737.511</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>Ngày 30 tháng 6 năm 2026</x:t>
+    <x:t>Ngày 31 tháng 8 năm 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Người lập biểu</x:t>
   </x:si>
   <x:si>
     <x:t>Giám đốc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>112</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">33.296.496 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.376.969.140</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.065.719.725</x:t>
-  </x:si>
-  <x:si>
-    <x:t>344.545.911</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -207,7 +248,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="8">
+  <x:cellStyleXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -226,6 +267,9 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -233,7 +277,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -284,6 +328,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -597,7 +653,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E11"/>
+  <x:dimension ref="A1:E17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -672,55 +728,147 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="B7" s="2"/>
-      <x:c r="C7" s="1" t="s">
+      <x:c r="A7" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
-        <x:v>13</x:v>
+      <x:c r="D7" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
-      <x:c r="B8" s="2"/>
-      <x:c r="C8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="A8" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
+      <x:c r="D8" s="15"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
-      <x:c r="B9" s="2"/>
-      <x:c r="C9" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s">
+      <x:c r="A9" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="E9" s="13" t="s">
+      <x:c r="C9" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="D9" s="15"/>
+      <x:c r="E9" s="15" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
-      <x:c r="C10" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="14"/>
+      <x:c r="A10" s="13">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E10" s="15"/>
     </x:row>
     <x:row r="11" spans="1:5">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="16"/>
+      <x:c r="A11" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E11" s="15"/>
+    </x:row>
+    <x:row r="12" spans="1:5">
+      <x:c r="A12" s="13">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D12" s="15"/>
+      <x:c r="E12" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:5">
+      <x:c r="B13" s="2"/>
+      <x:c r="C13" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:5">
+      <x:c r="B14" s="2"/>
+      <x:c r="C14" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:5">
+      <x:c r="B15" s="2"/>
+      <x:c r="C15" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:5">
+      <x:c r="C16" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D16" s="17"/>
+    </x:row>
+    <x:row r="17" spans="1:5">
+      <x:c r="B17" s="18" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D17" s="19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="7">
@@ -729,156 +877,8 @@
     <x:mergeCell ref="A3:E3"/>
     <x:mergeCell ref="A4:E4"/>
     <x:mergeCell ref="A5:C5"/>
-    <x:mergeCell ref="C10:D10"/>
-    <x:mergeCell ref="C11:D11"/>
-  </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:E11"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
-    <x:col min="1" max="1" width="5.710625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="40.710625" style="2" customWidth="1"/>
-    <x:col min="3" max="5" width="15.710625" style="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:5">
-      <x:c r="A1" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-    </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
-    </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="6"/>
-      <x:c r="C3" s="5"/>
-      <x:c r="D3" s="5"/>
-      <x:c r="E3" s="5"/>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B4" s="8"/>
-      <x:c r="C4" s="7"/>
-      <x:c r="D4" s="7"/>
-      <x:c r="E4" s="7"/>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="A5" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="8"/>
-      <x:c r="C5" s="7"/>
-      <x:c r="D5" s="9" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
-      <x:c r="A6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B6" s="12" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5">
-      <x:c r="B7" s="2"/>
-      <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E7" s="13" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
-      <x:c r="B8" s="2"/>
-      <x:c r="C8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="13" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E8" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:5">
-      <x:c r="B9" s="2"/>
-      <x:c r="C9" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:5">
-      <x:c r="C10" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="14"/>
-    </x:row>
-    <x:row r="11" spans="1:5">
-      <x:c r="B11" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="16"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A2:D2"/>
-    <x:mergeCell ref="A3:E3"/>
-    <x:mergeCell ref="A4:E4"/>
-    <x:mergeCell ref="A5:C5"/>
-    <x:mergeCell ref="C10:D10"/>
-    <x:mergeCell ref="C11:D11"/>
+    <x:mergeCell ref="C16:D16"/>
+    <x:mergeCell ref="C17:D17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
